--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2853" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2853" uniqueCount="331">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -841,6 +841,10 @@
     <t>ED.thumbnail</t>
   </si>
   <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
+  </si>
+  <si>
     <t>Observation.statusCode</t>
   </si>
   <si>
@@ -889,8 +893,8 @@
     <t>Observation.value</t>
   </si>
   <si>
-    <t>http://hl7.org/cda/stds/core/StructureDefinition/ANY
-http://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/CDhttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
+    <t>http://hl7.org/cda/stds/core/StructureDefinition/CD
+http://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/CShttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/INT-POShttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/ONhttp://hl7.org/cda/stds/core/StructureDefinition/PNhttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/TNhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-INThttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
   </si>
   <si>
     <t>Résultat de la demande</t>
@@ -7334,7 +7338,7 @@
         <v>74</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>74</v>
+        <v>265</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>74</v>
@@ -7342,10 +7346,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7371,10 +7375,10 @@
         <v>91</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7405,7 +7409,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7423,7 +7427,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7443,10 +7447,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7469,13 +7473,13 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7526,7 +7530,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7546,10 +7550,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7572,7 +7576,7 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7605,7 +7609,7 @@
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>74</v>
@@ -7623,7 +7627,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7643,10 +7647,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7669,7 +7673,7 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7722,7 +7726,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7742,10 +7746,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7801,25 +7805,25 @@
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7839,10 +7843,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7865,10 +7869,10 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
@@ -7920,7 +7924,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7940,10 +7944,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7966,13 +7970,13 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8003,7 +8007,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>74</v>
@@ -8021,7 +8025,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8041,10 +8045,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8067,13 +8071,13 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8104,7 +8108,7 @@
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>74</v>
@@ -8122,7 +8126,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8142,10 +8146,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8171,10 +8175,10 @@
         <v>171</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8225,7 +8229,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8245,10 +8249,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8271,7 +8275,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8324,7 +8328,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8344,10 +8348,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8370,7 +8374,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8423,7 +8427,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8443,10 +8447,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8469,7 +8473,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8522,7 +8526,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8542,10 +8546,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8568,13 +8572,13 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8625,7 +8629,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8645,10 +8649,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8671,7 +8675,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8724,7 +8728,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8744,10 +8748,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8770,7 +8774,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8823,7 +8827,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8843,10 +8847,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8869,7 +8873,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8922,7 +8926,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8942,10 +8946,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8968,7 +8972,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9021,7 +9025,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9041,10 +9045,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9067,7 +9071,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9120,7 +9124,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9140,10 +9144,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9166,7 +9170,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9219,7 +9223,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9239,10 +9243,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9265,11 +9269,11 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9320,7 +9324,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9340,10 +9344,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9441,10 +9445,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9542,10 +9546,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9643,10 +9647,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9744,10 +9748,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9847,10 +9851,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9950,10 +9954,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10053,10 +10057,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10156,10 +10160,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10257,10 +10261,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10294,7 +10298,7 @@
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="S88" t="s" s="2">
         <v>74</v>
@@ -10316,7 +10320,7 @@
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>74</v>
@@ -10334,7 +10338,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10354,10 +10358,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10380,7 +10384,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10433,7 +10437,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -10453,10 +10457,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10479,7 +10483,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10532,7 +10536,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
